--- a/项目管理系统-需求与优化记录.xlsx
+++ b/项目管理系统-需求与优化记录.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'需求与优化记录'!$A$1:$H$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'需求与优化记录'!$A$1:$J$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -573,20 +573,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>版本号</t>
@@ -594,336 +596,416 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>一级页面</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>二级页面</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>当前需求</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>需求时间</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>更新内容</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>更新时间</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="74" customHeight="1">
+    <row r="2" ht="76" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>v2.1</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>日历视图</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>月视图滚动区（月份轨道）、日历标题</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>日历视图支持上下滑动连续切换月份，不再依赖「上月/下月」按钮</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>新增「上月 / 当月 / 下月」三段月份轨道堆叠在同一纵向滚动区；滚动到轨道边缘自动重排续接，实现无限连续翻月；滚动时日历标题随视口顶部月份实时更新</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>月份轨道方案的前置需求，后续「月份块不重叠」在此基础上升级</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="74" customHeight="1">
+    <row r="3" ht="76" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>v2.1</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>日历视图</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>顶部工具栏与月份标题区（移动端断点）</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>移动端月视图顶部占位过高，首屏可见周数过少</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>压缩移动端日历工具栏与标题区间距、精简按钮排布，减少顶部留白，提升首屏可见的周数</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>仅移动端断点生效，桌面端布局不变</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="74" customHeight="1">
+    <row r="4" ht="76" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>v2.1</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>日历视图</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>月份滚动区手势、任务条拖拽/拉伸手势（移动端）</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>移动端滑动手势易误触发（翻月误触、拖拽任务条误触）</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>提高手势触发阈值、增加防抖与滑动方向判断、处理 pointercancel 中断事件，降低误触概率</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>与「轻点/双击打开任务弹窗」的判定逻辑配合使用</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="74" customHeight="1">
+    <row r="5" ht="76" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>v2.1</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>日历视图</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>月份块日期网格（周行与月份标题）</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>10 月与 11 月重复出现 10/26–11/6 两周，相邻月份块内容重叠</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>重构月份块周边界规则：一周归属给「其周一所在的月份」；每个月块先独立补齐首周（当月 1 号所在周）与末周（当月最后一天所在周），再对相邻块首尾重复行统一去重，实现零重叠、无间隙、日期严格连续</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>新增 _getMonthWeeks / _mondayToWeek / _weekMondayOf / _enrichMonthWeeks / _buildCalendarBlocks 等函数；提交 8f3c564</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="74" customHeight="1">
+    <row r="6" ht="76" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>v2.1</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>日历视图</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>月视图任务条拖拽落点计算（周行基准日期）</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>月份块行数由固定 6 行变为动态行数后，拖拽任务条定位的基准日期错位</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>渲染每个周行时写入 data-week-monday（该周周一日期），拖拽时直接读取该属性计算落点日期，替代原来「行号 + getMonthDates 切片」的隐式映射</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>与上一行配套的修复；保留无属性时的旧逻辑兜底</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="74" customHeight="1">
+    <row r="7" ht="76" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>v2.1</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>日历视图</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>日历滚动区初始定位（首行对齐 / 粘性月份标题）</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>日历视图默认第一行日期显示「当天所在的那一周」</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>新增 _alignRailToWeekOfToday：进入日历月视图或点击「今天」时，把当天所在周对齐到滚动区顶部（并扣除粘性月份标题高度）；锚点月不是当前月时退化为对齐该月顶部，避免浏览其他月份被强行拉回</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>同时移除失效的 _scrollToToday 标志位；提交 78d075c、25eee65</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="74" customHeight="1">
+    <row r="8" ht="76" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>v2.1</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>全局（工程与发布）</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>app/ 与根目录源文件、分享包打包、GitHub Pages</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>改动需同步到根目录并更新线上版本</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>app/ 与根目录的 app.js 保持一致，重新打包 .trae-html-share-packages 分享包，提交并推送到 origin/main（GitHub Pages 自动部署）</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>涉及 app.js、app/app.js 及两个分享包压缩文件</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H8"/>
+  <autoFilter ref="A1:J8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -935,14 +1017,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="84" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="24" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
           <t>字段</t>
@@ -957,94 +1039,118 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>版本号</t>
+          <t>一级页面</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>按迭代批次归纳：v2.1 为本次日历体验优化批次；可按实际版本规划自行调整</t>
+          <t>功能所属的一级页面，如：表格视图 / 日历视图 / 左侧项目结构 / 归档视图 / 全局（工程与发布）</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>当前需求</t>
+          <t>二级页面</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>用户提出的原始诉求（一句话概括）</t>
+          <t>该需求具体落在页面中的哪一块内容，如：月份块日期网格、顶部工具栏、任务条拖拽落点等</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>需求时间</t>
+          <t>版本号</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>需求提出日期；对话中未记录明确日期的以「—」占位，可按实际情况补充</t>
+          <t>按迭代批次归纳：v2.1 为本次日历体验优化批次；可按实际版本规划自行调整</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>优先级</t>
+          <t>当前需求</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>高 / 中 / 低</t>
+          <t>用户提出的原始诉求（一句话概括）</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>状态</t>
+          <t>需求时间</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>已完成 / 进行中 / 待开始</t>
+          <t>需求提出日期；对话中未记录明确日期的以「—」占位，可按实际情况补充</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>更新内容</t>
+          <t>优先级</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>实际落地到代码里的改动要点</t>
+          <t>高 / 中 / 低</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>更新时间</t>
+          <t>状态</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>完成并上线的日期；有 Git 提交记录的按提交时间填写</t>
+          <t>已完成 / 进行中 / 待开始</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
+          <t>更新内容</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>实际落地到代码里的改动要点</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>更新时间</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>完成并上线的日期；有 Git 提交记录的按提交时间填写</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>关联函数、提交号、依赖关系等补充信息</t>
         </is>
